--- a/data/results/diagnostic_cases/prepared_ieee14_required_case_summary.xlsx
+++ b/data/results/diagnostic_cases/prepared_ieee14_required_case_summary.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/tmp/CR-ES-data-code-clean-20260528.KqVCUA/data/results/diagnostic_cases/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A2DD7D-AB31-B348-8E9E-0C0FB5D6E6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="580" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>scenario</t>
   </si>
@@ -67,9 +73,6 @@
     <t>throughput_MWh</t>
   </si>
   <si>
-    <t>ES0_0MW</t>
-  </si>
-  <si>
     <t>ES40_30MW</t>
   </si>
   <si>
@@ -80,9 +83,6 @@
   </si>
   <si>
     <t>RGcap0xPeak_ES40_30MW</t>
-  </si>
-  <si>
-    <t>RGcap1xPeak_ES40_30MW</t>
   </si>
   <si>
     <t>RGcap2xPeak_ES40_30MW</t>
@@ -94,8 +94,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,13 +158,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -202,7 +210,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -236,6 +244,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -270,9 +279,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -445,11 +455,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -502,7 +512,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -510,52 +520,52 @@
         <v>72</v>
       </c>
       <c r="C2">
-        <v>325.926</v>
+        <v>325.92599999999999</v>
       </c>
       <c r="D2">
-        <v>18651.582</v>
+        <v>18651.581999999999</v>
       </c>
       <c r="E2">
         <v>1030</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>21.477267846075492</v>
       </c>
       <c r="I2">
-        <v>19430.16299796484</v>
+        <v>19430.162997964839</v>
       </c>
       <c r="J2">
-        <v>17146.14935290761</v>
+        <v>18081.04985522541</v>
       </c>
       <c r="K2">
-        <v>2284.013645057235</v>
+        <v>1349.11314273944</v>
       </c>
       <c r="L2">
-        <v>1505.43264709239</v>
+        <v>733.78558189617911</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1571.671683564455</v>
+        <v>766.07214749961099</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1107.341309896444</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>944.08787277486067</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2051.4291826713052</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -563,52 +573,52 @@
         <v>72</v>
       </c>
       <c r="C3">
-        <v>325.926</v>
+        <v>325.92599999999999</v>
       </c>
       <c r="D3">
-        <v>18651.582</v>
+        <v>18651.581999999999</v>
       </c>
       <c r="E3">
         <v>1030</v>
       </c>
       <c r="F3">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="G3">
-        <v>280</v>
+        <v>560</v>
       </c>
       <c r="H3">
-        <v>21.47726784607549</v>
+        <v>42.954535692150984</v>
       </c>
       <c r="I3">
-        <v>19430.16299796484</v>
+        <v>19430.162997964839</v>
       </c>
       <c r="J3">
-        <v>18081.04985522541</v>
+        <v>18843.901176566091</v>
       </c>
       <c r="K3">
-        <v>1349.11314273944</v>
+        <v>586.26182139875141</v>
       </c>
       <c r="L3">
-        <v>733.7855818961791</v>
+        <v>180.93559164139941</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3">
-        <v>766.072147499611</v>
+        <v>188.8967576736209</v>
       </c>
       <c r="O3">
-        <v>1107.341309896444</v>
+        <v>2432.4774093908532</v>
       </c>
       <c r="P3">
-        <v>944.0878727748607</v>
+        <v>2059.222641183359</v>
       </c>
       <c r="Q3">
-        <v>2051.429182671305</v>
+        <v>4491.7000505742117</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -616,105 +626,105 @@
         <v>72</v>
       </c>
       <c r="C4">
-        <v>325.926</v>
+        <v>325.92599999999999</v>
       </c>
       <c r="D4">
-        <v>18651.582</v>
+        <v>18651.581999999999</v>
       </c>
       <c r="E4">
         <v>1030</v>
       </c>
       <c r="F4">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="G4">
-        <v>560</v>
+        <v>960</v>
       </c>
       <c r="H4">
-        <v>42.95453569215098</v>
+        <v>73.636346900830233</v>
       </c>
       <c r="I4">
-        <v>19430.16299796484</v>
+        <v>19430.162997964839</v>
       </c>
       <c r="J4">
-        <v>18843.90117656609</v>
+        <v>19295.243505110291</v>
       </c>
       <c r="K4">
-        <v>586.2618213987514</v>
+        <v>134.91949285455911</v>
       </c>
       <c r="L4">
-        <v>180.9355916413994</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>188.8967576736209</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>2432.477409390853</v>
+        <v>4077.3758892181831</v>
       </c>
       <c r="P4">
-        <v>2059.222641183359</v>
+        <v>3433.7143841078969</v>
       </c>
       <c r="Q4">
-        <v>4491.700050574212</v>
+        <v>7511.09027332608</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>20</v>
       </c>
       <c r="B5">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C5">
-        <v>325.926</v>
+        <v>325.92599999999999</v>
       </c>
       <c r="D5">
-        <v>18651.582</v>
+        <v>6217.1940000000004</v>
       </c>
       <c r="E5">
-        <v>1030</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="G5">
-        <v>960</v>
+        <v>280</v>
       </c>
       <c r="H5">
-        <v>73.63634690083023</v>
+        <v>21.477267846075492</v>
       </c>
       <c r="I5">
-        <v>19430.16299796484</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>19295.24350511029</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>134.9194928545591</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>6229.679382066277</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>6503.7852748771929</v>
       </c>
       <c r="O5">
-        <v>4077.375889218183</v>
+        <v>127.2083820662768</v>
       </c>
       <c r="P5">
-        <v>3433.714384107897</v>
+        <v>114.723</v>
       </c>
       <c r="Q5">
-        <v>7511.09027332608</v>
+        <v>241.9313820662768</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -722,13 +732,13 @@
         <v>24</v>
       </c>
       <c r="C6">
-        <v>325.926</v>
+        <v>325.92599999999999</v>
       </c>
       <c r="D6">
-        <v>6217.194</v>
+        <v>6217.1940000000004</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="F6">
         <v>70</v>
@@ -737,37 +747,37 @@
         <v>280</v>
       </c>
       <c r="H6">
-        <v>21.47726784607549</v>
+        <v>21.477267846075492</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>4080.1324660151822</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>4080.1324660151822</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1.4210854715202001E-14</v>
       </c>
       <c r="L6">
-        <v>6229.679382066277</v>
+        <v>2160.108317610549</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>6503.785274877193</v>
+        <v>2255.1530835854128</v>
       </c>
       <c r="O6">
-        <v>127.2083820662768</v>
+        <v>152.046783625731</v>
       </c>
       <c r="P6">
-        <v>114.723</v>
+        <v>129</v>
       </c>
       <c r="Q6">
-        <v>241.9313820662768</v>
+        <v>281.046783625731</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -775,13 +785,13 @@
         <v>24</v>
       </c>
       <c r="C7">
-        <v>325.926</v>
+        <v>325.92599999999999</v>
       </c>
       <c r="D7">
-        <v>6217.194</v>
+        <v>6217.1940000000004</v>
       </c>
       <c r="E7">
-        <v>330</v>
+        <v>980</v>
       </c>
       <c r="F7">
         <v>70</v>
@@ -790,140 +800,34 @@
         <v>280</v>
       </c>
       <c r="H7">
-        <v>21.47726784607549</v>
+        <v>21.477267846075492</v>
       </c>
       <c r="I7">
-        <v>2069.303234522459</v>
+        <v>6166.893342355289</v>
       </c>
       <c r="J7">
-        <v>2069.303234522459</v>
+        <v>5759.5983497349807</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>407.29499262030771</v>
       </c>
       <c r="L7">
-        <v>4147.89076547754</v>
+        <v>500.25719666699229</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7">
-        <v>4330.397959158553</v>
+        <v>522.26851332033993</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>306.37356866854361</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>263.71202226657039</v>
       </c>
       <c r="Q7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8">
-        <v>24</v>
-      </c>
-      <c r="C8">
-        <v>325.926</v>
-      </c>
-      <c r="D8">
-        <v>6217.194</v>
-      </c>
-      <c r="E8">
-        <v>650</v>
-      </c>
-      <c r="F8">
-        <v>70</v>
-      </c>
-      <c r="G8">
-        <v>280</v>
-      </c>
-      <c r="H8">
-        <v>21.47726784607549</v>
-      </c>
-      <c r="I8">
-        <v>4080.132466015182</v>
-      </c>
-      <c r="J8">
-        <v>4080.132466015182</v>
-      </c>
-      <c r="K8">
-        <v>1.4210854715202E-14</v>
-      </c>
-      <c r="L8">
-        <v>2160.108317610549</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>2255.153083585413</v>
-      </c>
-      <c r="O8">
-        <v>152.046783625731</v>
-      </c>
-      <c r="P8">
-        <v>129</v>
-      </c>
-      <c r="Q8">
-        <v>281.046783625731</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9">
-        <v>24</v>
-      </c>
-      <c r="C9">
-        <v>325.926</v>
-      </c>
-      <c r="D9">
-        <v>6217.194</v>
-      </c>
-      <c r="E9">
-        <v>980</v>
-      </c>
-      <c r="F9">
-        <v>70</v>
-      </c>
-      <c r="G9">
-        <v>280</v>
-      </c>
-      <c r="H9">
-        <v>21.47726784607549</v>
-      </c>
-      <c r="I9">
-        <v>6166.893342355289</v>
-      </c>
-      <c r="J9">
-        <v>5759.598349734981</v>
-      </c>
-      <c r="K9">
-        <v>407.2949926203077</v>
-      </c>
-      <c r="L9">
-        <v>500.2571966669923</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>522.2685133203399</v>
-      </c>
-      <c r="O9">
-        <v>306.3735686685436</v>
-      </c>
-      <c r="P9">
-        <v>263.7120222665704</v>
-      </c>
-      <c r="Q9">
-        <v>570.0855909351138</v>
+        <v>570.08559093511383</v>
       </c>
     </row>
   </sheetData>
